--- a/01_data/02_processed_files/Rudd_tag_workbook.xlsx
+++ b/01_data/02_processed_files/Rudd_tag_workbook.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{48E38470-2CC8-4B55-B213-4944A3273FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B80960-5C48-4C18-9BF9-5B0530015A60}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B80960-5C48-4C18-9BF9-5B0530015A60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
